--- a/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
+++ b/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
@@ -284,10 +284,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Make a copy of the Raw sheet (right-click its tab → Move or Copy → tick Create a copy). On the copy, run Data → Remove Duplicates on the whole table with every column ticked except RecordID (each row has its own RecordID, so leaving it ticked finds nothing). How many duplicate rows does Excel remove?</t>
+          <t>Make a copy of the Raw sheet (right-click its tab → Move or Copy → tick Create a copy). On the copy, run Data → Remove Duplicates on all the data (A1:J651) with every column ticked except RecordID (each row has its own RecordID, so leaving it ticked finds nothing). How many duplicate rows does Excel remove?</t>
         </is>
       </c>
       <c r="C7" s="39" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Back on Clean, use Flash Fill to fill the yellow ZIP5 column (O) with the 5-digit ZIP from CityStateZip. 101 rows carry a ZIP+4 such as 45501-8106, and those must become 45501. Type the first two or three ZIPs yourself (include one ZIP+4 row), then press Ctrl + E. The gray cell counts the distinct ZIP codes in your column.</t>
+          <t>Back on Clean, use Flash Fill to fill the yellow ZIP5 column (O) with the 5-digit ZIP from CityStateZip. 101 rows carry a ZIP+4 such as 45501-8106, and those must become 45501. Type three examples yourself: rows 2 and 3, plus the first ZIP+4 row (row 11). Then select the first empty cell and press Ctrl + E (Mac: Data → Flash Fill). The gray cell counts the distinct ZIP codes in your column.</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="216" customHeight="1">
+    <row r="14" ht="246" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>10</t>
@@ -1488,11 +1488,11 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>FIND(",",B2) returns a position when there is a comma and #VALUE! when there isn't, so ISNUMBER(FIND(…)) tells the two layouts apart. For Last, First rows, MID takes everything after the comma (the first name) and LEFT takes everything before it (the last name). TRIM each piece before joining, because the spaces sit around the comma. PROPER on the outside fixes the case of both layouts at once. Two checks on the result: if you skip the flip, the count rises to 569, because the same patient appears as both "Amber White" (row 18) and "White Amber" (row 410). And the count is 557, not 560, because 3 names belong to two different patients (Justin Lewis, Lisa Morris, Mei Myers). That's why you dedupe on MRN, never on name. PROPER also turns McDonald into Mcdonald, so fix known exceptions by hand and note them in the cleaning log.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="231" customHeight="1">
+          <t>FIND(",",B2) returns a position when there is a comma and #VALUE! when there isn't, so ISNUMBER(FIND(…)) tells the two layouts apart. For Last, First rows, MID takes everything after the comma (the first name) and LEFT takes everything before it (the last name). TRIM each piece before joining, because the spaces sit around the comma. PROPER on the outside fixes the case of both layouts at once. Two checks on the result. First, the flip matters: =PROPER(TRIM(B2)) alone gives 578 distinct names, and deleting the comma without flipping still gives 569, because the same patient then appears as both "Amber White" (row 18) and "White Amber" (row 410). Second, the count is 557, not 560, because 3 names belong to two different patients (Justin Lewis, Lisa Morris, Mei Myers). That's why you dedupe on MRN, never on name. PROPER also turns McDonald into Mcdonald, so fix known exceptions by hand and note them in the cleaning log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="246" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>11</t>
@@ -1512,12 +1512,12 @@
         </is>
       </c>
       <c r="E15" cm="1" s="41">
-        <f t="array" ref="E15">SUMPRODUCT(--(DAY(DATEVALUE(SUBSTITUTE(Raw!C2:C651,".","/")))&gt;12))</f>
+        <f t="array" ref="E15">SUMPRODUCT(--(DAY(IF(MID(Raw!C2:C651,5,1)="-",DATE(LEFT(Raw!C2:C651,4),MID(Raw!C2:C651,6,2),RIGHT(Raw!C2:C651,2)),IF(MID(Raw!C2:C651,3,1)="-",DATE(RIGHT(Raw!C2:C651,4),(SEARCH(MID(Raw!C2:C651,4,3),"JanFebMarAprMayJunJulAugSepOctNovDec")+2)/3,LEFT(Raw!C2:C651,2)),DATE(RIGHT(Raw!C2:C651,4),LEFT(Raw!C2:C651,FIND("/",SUBSTITUTE(Raw!C2:C651,".","/"))-1),MID(Raw!C2:C651,FIND("/",SUBSTITUTE(Raw!C2:C651,".","/"))+1,LEN(Raw!C2:C651)-FIND("/",SUBSTITUTE(Raw!C2:C651,".","/"))-5)))))&gt;12))</f>
         <v/>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>This solution works on any computer: it reads the layout and builds DATE(year, month, day) from the pieces. ISO dates have a dash in position 5. In 03-Apr-1957 the dash is in position 3, and the month comes from where Apr sits in "JanFebMarAprMayJunJulAugSepOctNovDec" (position 10, and (10+2)/3 = 4). Everything else is month/day/year with a / or . after the month. If your Windows or Mac region is United States, the much shorter =DATEVALUE(SUBSTITUTE(C2,".","/")) gives identical results, because DATEVALUE reads the ISO and 03-Apr-1957 layouts everywhere and reads slashes month first. In a day-first region it reads 08/06/1989 as 8 June and fails on 3/22/1961. The day-13 test catches a swap: a month number is never above 12, so if the slash and dot rows had month and day swapped, none of them could show a day above 12 and the count would fall to 145 instead of 397.</t>
+          <t>This solution works on any computer: it reads the layout and builds DATE(year, month, day) from the pieces. ISO dates have a dash in position 5. In 03-Apr-1957 the dash is in position 3, and the month comes from where Apr sits in "JanFebMarAprMayJunJulAugSepOctNovDec" (position 10, and (10+2)/3 = 4). Everything else is month/day/year with a / or . after the month. If your Windows or Mac region is United States, the much shorter =DATEVALUE(SUBSTITUTE(C2,".","/")) gives identical results, because U.S. settings read the ISO and 03-Apr-1957 layouts and read slashes month first. In a day-first region it reads 08/06/1989 as 8 June and fails on 3/22/1961, and in a language whose month names differ from English it can fail on 03-Apr-1957 too. The day-13 test catches a swap: a month number is never above 12, so if the slash and dot rows had month and day swapped, none of them could show a day above 12 and the count would fall to 145 instead of 397.</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E5" cm="1" s="41">
-        <f t="array" ref="E5">SUMPRODUCT(--(HOUR(--Raw!J2:J651)&gt;=17))</f>
+        <f t="array" ref="E5">SUMPRODUCT(--(HOUR(IF(MID(Raw!J2:J651,5,1)="-",DATE(LEFT(Raw!J2:J651,4),MID(Raw!J2:J651,6,2),MID(Raw!J2:J651,9,2)),DATE(MID(Raw!J2:J651,7,4),LEFT(Raw!J2:J651,2),MID(Raw!J2:J651,4,2)))+TIMEVALUE(MID(Raw!J2:J651,12,8)))&gt;=17))</f>
         <v/>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="E7" cm="1" s="45">
-        <f t="array" ref="E7">MAX(IF(TEXT(VALUE(SUBSTITUTE(Raw!I2:I651,"MRN-","")),"00000000")="01276260",--Raw!J2:J651))</f>
+        <f t="array" ref="E7">MAX(IF(TEXT(VALUE(SUBSTITUTE(Raw!I2:I651,"MRN-","")),"00000000")="01276260",IF(MID(Raw!J2:J651,5,1)="-",DATE(LEFT(Raw!J2:J651,4),MID(Raw!J2:J651,6,2),MID(Raw!J2:J651,9,2)),DATE(MID(Raw!J2:J651,7,4),LEFT(Raw!J2:J651,2),MID(Raw!J2:J651,4,2)))+TIMEVALUE(MID(Raw!J2:J651,12,8))))</f>
         <v/>
       </c>
       <c r="F7" s="19" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Make a copy of the Raw sheet (right-click its tab → Move or Copy → tick Create a copy). On the copy, run Data → Remove Duplicates on the whole table with every column ticked except RecordID (each row has its own RecordID, so leaving it ticked finds nothing). How many duplicate rows does Excel remove?</t>
+          <t>Make a copy of the Raw sheet (right-click its tab → Move or Copy → tick Create a copy). On the copy, run Data → Remove Duplicates on all the data (A1:J651) with every column ticked except RecordID (each row has its own RecordID, so leaving it ticked finds nothing). How many duplicate rows does Excel remove?</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1944,7 +1944,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="81" customHeight="1">
+    <row r="10" ht="96" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>5</t>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Back on Clean, use Flash Fill to fill the yellow ZIP5 column (O) with the 5-digit ZIP from CityStateZip. 101 rows carry a ZIP+4 such as 45501-8106, and those must become 45501. Type the first two or three ZIPs yourself (include one ZIP+4 row), then press Ctrl + E. The gray cell counts the distinct ZIP codes in your column.</t>
+          <t>Back on Clean, use Flash Fill to fill the yellow ZIP5 column (O) with the 5-digit ZIP from CityStateZip. 101 rows carry a ZIP+4 such as 45501-8106, and those must become 45501. Type three examples yourself: rows 2 and 3, plus the first ZIP+4 row (row 11). Then select the first empty cell and press Ctrl + E (Mac: Data → Flash Fill). The gray cell counts the distinct ZIP codes in your column.</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>XLOOKUP(TRIM(H2), PayerMap Variant column, PayerMap PayerID column, "UNMAPPED")</t>
+          <t>XLOOKUP the TRIMmed Insurance value in tblPayerMap, and use XLOOKUP's if_not_found argument for UNMAPPED</t>
         </is>
       </c>
       <c r="D13" cm="1" s="23">
@@ -75991,15 +75991,11 @@
           <t>10 spellings of 2 values: F, f, ' F', Female, FEMALE, M, m, 'M ', Male, MALE</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>SexClean: =UPPER(LEFT(TRIM(D2),1))</t>
-        </is>
-      </c>
-      <c r="E3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="34" t="n"/>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Practice task 12</t>
+          <t>Practice tasks 2 and 12</t>
         </is>
       </c>
     </row>
@@ -76017,8 +76013,8 @@
           <t>Two layouts (Last, First and First Last), stray spaces, ALL CAPS and lowercase</t>
         </is>
       </c>
-      <c r="D4" s="34" t="n"/>
-      <c r="E4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="34" t="n"/>
       <c r="F4" s="7" t="n"/>
     </row>
     <row r="5">
@@ -76035,8 +76031,8 @@
           <t>Six layouts, some with a +1 country code, and some blanks</t>
         </is>
       </c>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="34" t="n"/>
       <c r="F5" s="7" t="n"/>
     </row>
     <row r="6">
@@ -76053,8 +76049,8 @@
           <t>Leading zeros lost on some rows; MRN- prefix on others</t>
         </is>
       </c>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="34" t="n"/>
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
@@ -76071,8 +76067,8 @@
           <t>Dates stored as text in five layouts</t>
         </is>
       </c>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="33" t="n"/>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="34" t="n"/>
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
@@ -76089,8 +76085,8 @@
           <t>Many spellings of 7 payers, some with trailing spaces</t>
         </is>
       </c>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="34" t="n"/>
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
@@ -76107,8 +76103,8 @@
           <t>ZIP+4 mixed with 5-digit ZIPs</t>
         </is>
       </c>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="33" t="n"/>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="34" t="n"/>
       <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
@@ -76125,8 +76121,8 @@
           <t>Exact copies and re-registrations of the same patient</t>
         </is>
       </c>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="33" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="34" t="n"/>
       <c r="F10" s="7" t="n"/>
     </row>
     <row r="12">

--- a/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
+++ b/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
@@ -1208,11 +1208,11 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>TRIM removes leading and trailing spaces and shrinks inner runs to one space, so any name it shortens had extra spaces. Comparing lengths tests all 650 rows at once: the comparison gives TRUE/FALSE for each row, the double minus turns those into 1/0, and SUMPRODUCT adds them. You can't see a trailing space by looking at a cell, so a count like this is how you find out a problem exists before you fix it. (In Microsoft 365, =SUM(--(LEN(…)&lt;&gt;LEN(TRIM(…)))) works too.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="111" customHeight="1">
+          <t>TRIM removes leading and trailing spaces and shrinks inner runs to one space, so any name it shortens had extra spaces. Comparing lengths tests all 650 rows at once: the comparison gives TRUE/FALSE for each row, the double minus turns those into 1/0, and SUMPRODUCT adds them. You can't see a trailing space by looking at a cell, so a count like this is how you find out a problem exists before you fix it. In Microsoft 365, =SUM(--(LEN(…)&lt;&gt;LEN(TRIM(…)))) works too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="126" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>2</t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>Every spelling starts with the right letter once the stray space is gone, so the fix is TRIM → LEFT(…,1) → UPPER. The order matters: LEFT(" F",1) is a space. The check uses EXACT because COUNTIF ignores case and would count a lowercase f as F. This shortcut works only because each value is identified by its first letter. Medicare and Medicaid share a first letter, so Insurance needs a mapping table instead (task 8).</t>
+          <t>Every spelling starts with the right letter once the stray space is gone, so the fix is TRIM, then LEFT(…,1), then UPPER. The order matters: LEFT(" F",1) is a space. The check uses EXACT because COUNTIF ignores case and would count a lowercase f as F. This shortcut works only because each value is identified by its first letter. Medicare and Medicaid share a first letter, so Insurance needs a mapping table instead (task 8).</t>
         </is>
       </c>
     </row>
@@ -1257,11 +1257,11 @@
       </c>
       <c r="D7" s="40" t="inlineStr">
         <is>
-          <t>1. Right-click the **Raw** tab → **Move or Copy…** → tick **Create a copy** → **OK**. Work on **Raw (2)**.
-2. Click any cell in the data, then **Data → Remove Duplicates**.
-3. Keep **My data has headers** ticked. Untick **RecordID** and leave the other nine columns ticked. Click **OK**.
-4. Excel reports *40 duplicate values found and removed; 610 unique values remain.*
-Formula check without deleting anything (Microsoft 365 / Excel 2021+): `=ROWS(Raw!B2:J651)-ROWS(UNIQUE(Raw!B2:J651))`</t>
+          <t>1. Right-click the Raw tab → Move or Copy… → tick Create a copy → OK. Work on Raw (2).
+2. Click any cell in the data, then Data → Remove Duplicates.
+3. Keep My data has headers ticked. Untick RecordID and leave the other nine columns ticked. Click OK.
+4. Excel reports 40 duplicate values found and removed; 610 unique values remain.
+Formula check without deleting anything (Microsoft 365 / Excel 2021+): =ROWS(Raw!B2:J651)-ROWS(UNIQUE(Raw!B2:J651))</t>
         </is>
       </c>
       <c r="E7" cm="1" s="41">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="D8" s="40" t="inlineStr">
         <is>
-          <t>1. Select **A2:B50** on CensusExport (not the whole columns, and not the header row).
-2. **Home → Find &amp; Select → Go To Special…** (or press **F5**, Mac: **⌃ + G**, then **Special…**). Choose **Blanks** → **OK**. Only the empty cells stay selected.
-3. Without clicking anywhere, type **=** and press **↑**. The active cell is the first blank, A3, so the formula reads `=A2`.
-4. Press **Ctrl + Enter** (Mac: **⌘ + Return**) to put that formula in every selected blank. Each copy points to the cell above itself.
-5. Turn the formulas into values: select A2:B50, copy, then **Paste Special → Values**.
-Check with `=SUMIFS(CensusExport!E2:E50,CensusExport!A2:A50,"Cedar Ridge Medical Center",CensusExport!B2:B50,"Intensive Care Unit")`</t>
+          <t>1. Select A2:B50 on CensusExport (not the whole columns, and not the header row).
+2. Home → Find &amp; Select → Go To Special… (or press F5, Mac: ⌃ + G, then Special…). Choose Blanks → OK. Only the empty cells stay selected.
+3. Without clicking anywhere, type = and press ↑. The active cell is the first blank, A3, so the formula reads =A2.
+4. Press Ctrl + Enter (Mac: ⌘ + Return) to put that formula in every selected blank. Each copy points to the cell above itself.
+5. Turn the formulas into values: select A2:B50, copy, then Paste Special → Values.
+Check with =SUMIFS(CensusExport!E2:E50,CensusExport!A2:A50,"Cedar Ridge Medical Center",CensusExport!B2:B50,"Intensive Care Unit")</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -1325,11 +1325,11 @@
       </c>
       <c r="D9" s="40" t="inlineStr">
         <is>
-          <t>1. In **O2** type **45501** (from *Bluestone OH 45501*), and in **O3** type **45720** (from *CEDAR RIDGE, OH 45720*).
-2. In the first ZIP+4 row, **O11** (*Bluestone, OH 45501-8106*), type **45501**.
-3. Select **O4**, the first empty cell, and press **Ctrl + E** (or **Data → Flash Fill**).
-4. Check the result: `=SUMPRODUCT(--(LEN(Clean!O2:O651)&lt;&gt;5))` should return 0. If some rows are wrong, press Ctrl + Z, type the correct ZIP on one of the wrong rows as an extra example, and run Flash Fill again.
-Formula alternative (Microsoft 365): `=LEFT(TEXTAFTER(G2," ",-1),5)`</t>
+          <t>1. In O2 type 45501 (from Bluestone OH 45501), and in O3 type 45720 (from CEDAR RIDGE, OH 45720).
+2. In the first ZIP+4 row, O11 (Bluestone, OH 45501-8106), type 45501.
+3. Select O4, the first empty cell, and press Ctrl + E (or Data → Flash Fill).
+4. Check the result: =SUMPRODUCT(--(LEN(Clean!O2:O651)&lt;&gt;5)) should return 0. If some rows are wrong, press Ctrl + Z, type the correct ZIP on one of the wrong rows as an extra example, and run Flash Fill again.
+Formula alternative (Microsoft 365): =LEFT(TEXTAFTER(G2," ",-1),5)</t>
         </is>
       </c>
       <c r="E9" cm="1" s="41">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Flash Fill looks for a rule that explains every example you typed. Two plain ZIPs fit several rules (the first number, the last number, the last five characters), and on 45501-8106 those give different answers. The ZIP+4 example leaves only "the first number". If the +4 survives, the distinct count jumps to 108. Flash Fill writes typed-in values, not formulas, so it won't update when next month's export arrives. In Lesson 2.2 you did the same job with TEXTAFTER. The formula is the repeatable choice, and Flash Fill is the fast one for a one-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="141" customHeight="1">
+          <t>Flash Fill looks for a rule that explains every example you typed. Two plain ZIPs fit several rules (the first number, the last number, the last five characters), and on 45501-8106 those give different answers. The ZIP+4 example leaves only "the first number". If the +4 survives, the distinct count jumps to 108. Flash Fill writes typed-in values, not formulas, so it won't update when next month's export arrives. The Lesson 2.2 bonus did the same job with TEXTAFTER. The formula is the repeatable choice, and Flash Fill is the fast one for a one-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="156" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>6</t>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>Each SUBSTITUTE deletes one kind of character: parentheses, dashes, dots, and spaces. That leaves 5554767432 for most rows, but +15555973811 for the 40 numbers with a country code, so RIGHT(…,10) keeps the last ten digits, which is always the U.S. number. A blank phone stays empty, and the 30 blanks are why the count is 620, not 650. Keep phones as text: they are identifiers, not quantities. In Microsoft 365, =RIGHT(REGEXREPLACE(E2,"[^0-9]",""),10) removes every non-digit in one step.</t>
+          <t>Each SUBSTITUTE deletes one kind of character: parentheses, dashes, dots, and spaces. That leaves 5554767432 for most rows, but +15555973811 for the 40 numbers with a country code, so RIGHT(…,10) keeps the last ten digits, which is always the U.S. number. A blank phone needs no special handling, because SUBSTITUTE and RIGHT on an empty cell return an empty result. The 30 blanks are why the count is 620, not 650. Keep phones as text, because they are identifiers, not quantities. In Microsoft 365, =RIGHT(REGEXREPLACE(E2,"[^0-9]",""),10) removes every non-digit in one step.</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>A mapping table turns a messy category into a standard code with one lookup, and it documents your decisions where everyone can see them, such as Uninsured → PY07 Self-Pay. XLOOKUP ignores case, so the map needs only one row per spelling, not one per capitalization. It does not ignore spaces, so TRIM comes first. Without TRIM, the 12 rows typed "Silverline Medicare Advantage " with a trailing space come back UNMAPPED. The "UNMAPPED" result makes new spellings easy to find next month: filter for it, add the spelling as a new row of the map, and every formula picks it up. The Table references (tblPayerMap[Variant]) grow with the map. A fixed range such as PayerMap!$A$2:$A$20 works today but would miss a row added below it. Without XLOOKUP: =IFNA(VLOOKUP(TRIM(H2),tblPayerMap,2,FALSE),"UNMAPPED").</t>
+          <t>A mapping table turns a messy category into a standard code with one lookup, and it documents your decisions where everyone can see them, such as the rule that Uninsured means PY07 (Self-Pay). XLOOKUP ignores case, so the map needs only one row per spelling, not one per capitalization. It does not ignore spaces, so TRIM comes first. Without TRIM, the 12 rows typed "Silverline Medicare Advantage " with a trailing space come back UNMAPPED. The "UNMAPPED" result makes new spellings easy to find next month: filter for it, add the spelling as a new row of the map, and every formula picks it up. The Table references (tblPayerMap[Variant]) grow with the map. A fixed range such as PayerMap!$A$2:$A$20 works today but would miss a row added below it. Without XLOOKUP, use =IFNA(VLOOKUP(TRIM(H2),tblPayerMap,2,FALSE),"UNMAPPED").</t>
         </is>
       </c>
     </row>
@@ -1445,11 +1445,11 @@
       </c>
       <c r="D13" s="40" t="inlineStr">
         <is>
-          <t>1. On **LabFeed**, select **A1:A117** (header included).
-2. **Data → Text to Columns**. Choose **Delimited** → **Next**.
-3. Untick **Tab**, tick **Other**, and type a vertical bar **|** in the box. The preview splits into five columns. Click **Next**.
-4. Click the **MRN** column in the preview and choose **Text** as its column data format. Optionally click the last column and choose **Date: MDY**. Click **Finish**.
-Check with `=AVERAGEIF(LabFeed!B2:B117,"K",LabFeed!C2:C117)`</t>
+          <t>1. On LabFeed, select A1:A117 (header included).
+2. Data → Text to Columns. Choose Delimited → Next.
+3. Untick Tab, tick Other, and type a vertical bar | in the box. The preview splits into five columns. Click Next.
+4. Click the MRN column in the preview and choose Text as its column data format. Optionally click the last column and choose Date: MDY. Click Finish.
+Check with =AVERAGEIF(LabFeed!B2:B117,"K",LabFeed!C2:C117)</t>
         </is>
       </c>
       <c r="E13" cm="1" s="43">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Fill the yellow NameClean column (K) with every name as First Last in Proper Case, with single spaces: "Haddad, Jonathan" → Jonathan Haddad, "  Alexander ,  Gary " → Gary Alexander, and "Amber White" stays Amber White. 92 rows are already First Last (no comma). The gray cell warns if any name still has extra spaces or is ALL CAPS or all lowercase. Otherwise it counts distinct names.</t>
+          <t>Fill the yellow NameClean column (K) with every name as First Last in Proper Case, with single spaces. For example, "Haddad, Jonathan" becomes Jonathan Haddad, "  Alexander ,  Gary " becomes Gary Alexander, and "Amber White" stays Amber White. 92 rows are already First Last (no comma). The gray cell warns if any name still has extra spaces or is ALL CAPS or all lowercase. Otherwise it counts distinct names.</t>
         </is>
       </c>
       <c r="C14" s="39" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>FIND(",",B2) returns a position when there is a comma and #VALUE! when there isn't, so ISNUMBER(FIND(…)) tells the two layouts apart. For Last, First rows, MID takes everything after the comma (the first name) and LEFT takes everything before it (the last name). TRIM each piece before joining, because the spaces sit around the comma. PROPER on the outside fixes the case of both layouts at once. Two checks on the result. First, the flip matters: =PROPER(TRIM(B2)) alone gives 578 distinct names, and deleting the comma without flipping still gives 569, because the same patient then appears as both "Amber White" (row 18) and "White Amber" (row 410). Second, the count is 557, not 560, because 3 names belong to two different patients (Justin Lewis, Lisa Morris, Mei Myers). That's why you dedupe on MRN, never on name. PROPER also turns McDonald into Mcdonald, so fix known exceptions by hand and note them in the cleaning log.</t>
+          <t>FIND(",",B2) returns a position when there is a comma and #VALUE! when there isn't, so ISNUMBER(FIND(…)) tells the two layouts apart. For Last, First rows, MID takes everything after the comma (the first name) and LEFT takes everything before it (the last name). TRIM each piece before joining, because the spaces sit around the comma. PROPER on the outside fixes the case of both layouts at once. Two checks on the result. First, the flip matters: =PROPER(TRIM(B2)) alone gives 578 distinct names, and deleting the comma without flipping still gives 569, because the same patient then appears as both "Amber White" (row 18) and "White Amber" (row 410). Second, the count is 557, not 560, because 3 names belong to two different patients (Justin Lewis, Lisa Morris, Mei Myers). That's why you deduplicate on MRN, never on name. PROPER also turns McDonald into Mcdonald, so fix known exceptions by hand and note them in the cleaning log.</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="111" customHeight="1">
+    <row r="16" ht="126" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>12</t>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>A cleaning log records what you changed and how much, so the next person (or you, next month) can repeat it and audit it. "Rows changed" is the most useful number in it: here 424 of 650 rows changed and 226 were already F or M. EXACT matters again: with =, "f" equals "F" and those rows would look unchanged. A count that is suspiciously high or low is often the first sign that a cleaning formula is wrong.</t>
+          <t>A cleaning log records what you changed and how much, so the next person (or you, next month) can repeat it and audit it. "Rows changed" is the most useful number in it: here 424 of 650 rows changed and 226 were already F or M. EXACT matters again, because with = the values "f" and "F" count as equal and those rows would look unchanged. A count that is suspiciously high or low is often the first sign that a cleaning formula is wrong.</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="126" customHeight="1">
+    <row r="5" ht="141" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>B1</t>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>Both layouts put the time at character 12, so TIMEVALUE(MID(J2,12,8)) reads "18:33:00" and "05:42 PM" alike, and AM/PM is handled for you. The date part differs, so the IF builds it with DATE from the right pieces. A date-time is just date + time (a whole number plus a fraction of a day). If PM were ignored, the evening count would drop to 76. With U.S. regional settings, =--J2 (or =VALUE(J2)) converts both layouts in one step.</t>
+          <t>Both layouts put the time at character 12, so TIMEVALUE(MID(J2,12,8)) reads "18:33:00" and "05:42 PM" alike, and AM/PM is handled for you. The date part differs, so the IF builds it with DATE from the right pieces. In the ISO layout the day is MID(J2,9,2), not RIGHT(J2,2), because the time follows it. A date-time is just date + time (a whole number plus a fraction of a day). If PM were ignored, the evening count would drop to 76. With U.S. regional settings, =--J2 (or =VALUE(J2)) converts both layouts in one step.</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>The first test, RegisteredClean = MAXIFS(all RegisteredClean, all MRNClean, this MRN), is TRUE on the patient's latest row. Exact copies share that time, so the second test counts how many rows so far (the range $Q$2:Q2 grows as the formula goes down) have this MRN and this time. It equals 1 only on the first of them. The total must equal the 560 distinct MRNs from practice task 7, which is a good cross-check. Avoid comparing date-times with "&gt;"&amp;R2 inside COUNTIFS: that turns the time into text with 15 digits and can miss by a rounding error.</t>
+          <t>The first test, RegisteredClean = MAXIFS(all RegisteredClean, all MRNClean, this MRN), is TRUE on the patient's latest row. Exact copies share that time, so the second test counts how many rows so far (the range $Q$2:Q2 grows as the formula goes down) have this MRN and this time. It equals 1 only on the first of them. The total must equal the 560 distinct MRNs from practice task 7, which is a good cross-check. Avoid comparing date-times with "&gt;"&amp;R2 inside COUNTIFS, because that turns the time into text with 15 digits and can miss by a rounding error.</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="141" customHeight="1">
+    <row r="9" ht="171" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B5</t>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Survivorship check: "keep the latest row" can throw away good data. How many kept rows have an empty PhoneClean even though another registration for the same patient has a phone number?</t>
+          <t>The rule "keep the latest row" decides which registration survives into the master list, and it can throw away good data. How many kept rows have an empty PhoneClean even though another registration for the same patient has a phone number?</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>When its criteria argument is a range instead of a single value, COUNTIFS returns one count per row: how many rows share this row's MRN and have a phone. "?*" means at least one character, which works because PhoneClean is text. Multiply by Keep and by an empty PhoneClean to find the 2 patients who would arrive in the new EHR with no phone, although an older registration has one. Real MPI loads use survivorship rules for this: take each field from the most recent row that has it filled in, not every field from the most recent row.</t>
+          <t>When its criteria argument is a range instead of a single value, COUNTIFS returns one count per row: how many rows share this row's MRN and have a phone. The criteria "?*" means at least one character, which works because PhoneClean is text. Multiply by Keep and by an empty PhoneClean to find the 2 patients who would arrive in the new EHR with no phone, although an older registration has one. Real master patient index (MPI) loads prevent this with survivorship rules, which decide field by field which value survives. A common rule takes each field from the most recent row that has it filled in, instead of taking every field from the most recent row.</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Go To Special selects only the blanks; Ctrl + Enter fills them all with one relative formula</t>
+          <t>Go To Special selects only the blanks, and Ctrl + Enter fills them all with one relative formula</t>
         </is>
       </c>
       <c r="D9" cm="1" s="23">
@@ -2069,7 +2069,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="81" customHeight="1">
+    <row r="15" ht="96" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>10</t>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Fill the yellow NameClean column (K) with every name as First Last in Proper Case, with single spaces: "Haddad, Jonathan" → Jonathan Haddad, "  Alexander ,  Gary " → Gary Alexander, and "Amber White" stays Amber White. 92 rows are already First Last (no comma). The gray cell warns if any name still has extra spaces or is ALL CAPS or all lowercase. Otherwise it counts distinct names.</t>
+          <t>Fill the yellow NameClean column (K) with every name as First Last in Proper Case, with single spaces. For example, "Haddad, Jonathan" becomes Jonathan Haddad, "  Alexander ,  Gary " becomes Gary Alexander, and "Amber White" stays Amber White. 92 rows are already First Last (no comma). The gray cell warns if any name still has extra spaces or is ALL CAPS or all lowercase. Otherwise it counts distinct names.</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>EXACT compares case-sensitively; NOT flips it; SUMPRODUCT(--…) counts</t>
+          <t>EXACT compares case-sensitively, NOT flips TRUE and FALSE, and SUMPRODUCT(--…) counts the TRUEs</t>
         </is>
       </c>
       <c r="D17" cm="1" s="23">
@@ -76046,7 +76046,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Leading zeros lost on some rows; MRN- prefix on others</t>
+          <t>Leading zeros lost on some rows, and an MRN- prefix on others</t>
         </is>
       </c>
       <c r="D6" s="33" t="n"/>
@@ -76167,7 +76167,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Bluestone is moving to a new EHR, and the vendor needs a master patient load file with exactly one row per patient. The rule from Patient Access is: keep each patient's most recent registration (latest RegisteredOn). Work on the Clean sheet's last two yellow columns (RegisteredClean and Keep), using your MRNClean and PhoneClean columns from the practice tasks, then answer on the Bonus sheet. RegisteredOn has two layouts: 2015-11-06 18:33:00 (24-hour clock) and 05/30/2022 05:42 PM (12-hour clock).</t>
+          <t>Bluestone is moving to a new EHR, and the vendor needs a master patient load file with exactly one row per patient. The rule from Patient Access is: keep each patient's most recent registration (latest RegisteredOn). Fill the Clean sheet's last two yellow columns (RegisteredClean and Keep), using your MRNClean and PhoneClean columns from the practice tasks. RegisteredOn has two layouts: 2015-11-06 18:33:00 (24-hour clock) and 05/30/2022 05:42 PM (12-hour clock). If you want helper columns, put them on the Clean sheet in column V or further right, outside the Table.</t>
         </is>
       </c>
     </row>
@@ -76224,7 +76224,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>In both layouts the time starts at character 12, and TIMEVALUE understands both 18:33:00 and 05:42 PM. Build the date part with DATE</t>
+          <t>In both layouts the time starts at character 12, and TIMEVALUE understands both 18:33:00 and 05:42 PM. Build the date part with DATE, then add the time to it</t>
         </is>
       </c>
       <c r="D6" cm="1" s="23">
@@ -76249,7 +76249,7 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>MAXIFS finds the patient's latest time. A COUNTIFS over an expanding range ($Q$2:Q2) breaks ties</t>
+          <t>MAXIFS (Lesson 2.5) finds the patient's latest time. A COUNTIFS over an expanding range ($Q$2:Q2) breaks ties</t>
         </is>
       </c>
       <c r="D7" cm="1" s="23">
@@ -76261,7 +76261,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B3</t>
@@ -76274,7 +76274,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>MAXIFS (or XLOOKUP) with two conditions: this MRN, and Keep = TRUE</t>
+          <t>MAXIFS with two conditions: MRNClean is this MRN, and Keep is TRUE. Or filter Clean on those two columns and read RegisteredClean</t>
         </is>
       </c>
       <c r="D8" s="35" t="n"/>
@@ -76296,7 +76296,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>A row is a patient's first occurrence when MATCH(its MRN, the MRN column, 0) returns its own position. Or add a helper column with COUNTIF($Q$2:Q2,Q2)=1</t>
+          <t>A row is a patient's first occurrence when MATCH(its MRN, the MRN column, 0) returns its own position. Or add a helper column with =COUNTIF($Q$2:Q2,Q2)=1</t>
         </is>
       </c>
       <c r="D9" s="21" t="n"/>
@@ -76305,7 +76305,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="51" customHeight="1">
+    <row r="10" ht="66" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>B5</t>
@@ -76313,7 +76313,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Survivorship check: "keep the latest row" can throw away good data. How many kept rows have an empty PhoneClean even though another registration for the same patient has a phone number?</t>
+          <t>The rule "keep the latest row" decides which registration survives into the master list, and it can throw away good data. How many kept rows have an empty PhoneClean even though another registration for the same patient has a phone number?</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">

--- a/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
+++ b/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -303,20 +303,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -881,7 +878,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -889,7 +886,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -981,7 +978,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1002,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1034,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 650 rows — Excel Table 'tblClean'</t>
+          <t>Data: 650 rows, in the Excel Table 'tblClean'</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1046,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 19 rows — Excel Table 'tblPayerMap'</t>
+          <t>Data: 19 rows, in the Excel Table 'tblPayerMap'</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1082,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 9 rows — Excel Table 'tblLog'</t>
+          <t>Data: 9 rows, in the Excel Table 'tblLog'</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1130,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1147,7 +1144,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1199,7 @@
           <t>=SUMPRODUCT(--(LEN(Raw!B2:B651)&lt;&gt;LEN(TRIM(Raw!B2:B651))))</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="41">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">SUMPRODUCT(--(LEN(Raw!B2:B651)&lt;&gt;LEN(TRIM(Raw!B2:B651))))</f>
         <v/>
       </c>
@@ -1231,7 +1228,7 @@
           <t>=UPPER(LEFT(TRIM(D2),1))</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="41">
+      <c r="E6" cm="1" s="19">
         <f t="array" ref="E6">SUMPRODUCT(--EXACT(UPPER(LEFT(TRIM(Raw!D2:D651),1)),"F"))</f>
         <v/>
       </c>
@@ -1241,7 +1238,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="216" customHeight="1">
+    <row r="7" ht="201" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>3</t>
@@ -1264,7 +1261,7 @@
 Formula check without deleting anything (Microsoft 365 / Excel 2021+): =ROWS(Raw!B2:J651)-ROWS(UNIQUE(Raw!B2:J651))</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="41">
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">ROWS(Raw!B2:J651)-ROWS(_xlfn.UNIQUE(Raw!B2:J651))</f>
         <v/>
       </c>
@@ -1332,7 +1329,7 @@
 Formula alternative (Microsoft 365): =LEFT(TEXTAFTER(G2," ",-1),5)</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="41">
+      <c r="E9" cm="1" s="19">
         <f t="array" ref="E9">ROWS(_xlfn.UNIQUE(MID(Raw!G2:G651,FIND(" OH ",Raw!G2:G651)+4,5)))</f>
         <v/>
       </c>
@@ -1361,7 +1358,7 @@
           <t>=RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E2,"(",""),")",""),"-",""),".","")," ",""),10)</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="41">
+      <c r="E10" cm="1" s="19">
         <f t="array" ref="E10">SUMPRODUCT((LEN(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Raw!E2:E651,"(",""),")",""),"-",""),".","")," ",""),10))=10)*ISNUMBER(--RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Raw!E2:E651,"(",""),")",""),"-",""),".","")," ",""),10)))</f>
         <v/>
       </c>
@@ -1390,7 +1387,7 @@
           <t>=TEXT(VALUE(SUBSTITUTE(I2,"MRN-","")),"00000000")</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="41">
+      <c r="E11" cm="1" s="19">
         <f t="array" ref="E11">ROWS(_xlfn.UNIQUE(TEXT(VALUE(SUBSTITUTE(Raw!I2:I651,"MRN-","")),"00000000")))</f>
         <v/>
       </c>
@@ -1419,7 +1416,7 @@
           <t>=XLOOKUP(TRIM(H2),tblPayerMap[Variant],tblPayerMap[PayerID],"UNMAPPED")</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="41">
+      <c r="E12" cm="1" s="19">
         <f t="array" ref="E12">SUMPRODUCT(--(_xlfn.XLOOKUP(TRIM(Raw!H2:H651),PayerMap!$A$2:$A$20,PayerMap!$B$2:$B$20,"UNMAPPED")="PY02"))</f>
         <v/>
       </c>
@@ -1440,7 +1437,7 @@
           <t>Switch to LabFeed: 116 STAT results from a lab interface, each crammed into one cell as MRN|TestCode|Result|Units|CollectedDateTime. Split A1:A117 into five columns with Data → Text to Columns (Delimited, Other: |). In step 3 of the wizard, set the MRN column's format to Text so its leading zeros survive. The gray cell checks the MRNs, then shows the average potassium (TestCode K) result in mmol/L.</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n">
+      <c r="C13" s="41" t="n">
         <v>4.18125</v>
       </c>
       <c r="D13" s="40" t="inlineStr">
@@ -1452,7 +1449,7 @@
 Check with =AVERAGEIF(LabFeed!B2:B117,"K",LabFeed!C2:C117)</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="43">
+      <c r="E13" cm="1" s="42">
         <f t="array" ref="E13">AVERAGE(IF(MID(LabFeed!A2:A117,FIND("|",LabFeed!A2:A117)+1,FIND("|",LabFeed!A2:A117,FIND("|",LabFeed!A2:A117)+1)-FIND("|",LabFeed!A2:A117)-1)="K",--MID(LabFeed!A2:A117,FIND("|",LabFeed!A2:A117,FIND("|",LabFeed!A2:A117)+1)+1,FIND("|",LabFeed!A2:A117,FIND("|",LabFeed!A2:A117,FIND("|",LabFeed!A2:A117)+1)+1)-FIND("|",LabFeed!A2:A117,FIND("|",LabFeed!A2:A117)+1)-1)))</f>
         <v/>
       </c>
@@ -1511,7 +1508,7 @@
           <t>=IF(MID(C2,5,1)="-",DATE(LEFT(C2,4),MID(C2,6,2),RIGHT(C2,2)),IF(MID(C2,3,1)="-",DATE(RIGHT(C2,4),(SEARCH(MID(C2,4,3),"JanFebMarAprMayJunJulAugSepOctNovDec")+2)/3,LEFT(C2,2)),DATE(RIGHT(C2,4),LEFT(C2,FIND("/",SUBSTITUTE(C2,".","/"))-1),MID(C2,FIND("/",SUBSTITUTE(C2,".","/"))+1,LEN(C2)-FIND("/",SUBSTITUTE(C2,".","/"))-5))))</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="41">
+      <c r="E15" cm="1" s="19">
         <f t="array" ref="E15">SUMPRODUCT(--(DAY(IF(MID(Raw!C2:C651,5,1)="-",DATE(LEFT(Raw!C2:C651,4),MID(Raw!C2:C651,6,2),RIGHT(Raw!C2:C651,2)),IF(MID(Raw!C2:C651,3,1)="-",DATE(RIGHT(Raw!C2:C651,4),(SEARCH(MID(Raw!C2:C651,4,3),"JanFebMarAprMayJunJulAugSepOctNovDec")+2)/3,LEFT(Raw!C2:C651,2)),DATE(RIGHT(Raw!C2:C651,4),LEFT(Raw!C2:C651,FIND("/",SUBSTITUTE(Raw!C2:C651,".","/"))-1),MID(Raw!C2:C651,FIND("/",SUBSTITUTE(Raw!C2:C651,".","/"))+1,LEN(Raw!C2:C651)-FIND("/",SUBSTITUTE(Raw!C2:C651,".","/"))-5)))))&gt;12))</f>
         <v/>
       </c>
@@ -1540,7 +1537,7 @@
           <t>=SUMPRODUCT(--NOT(EXACT(Clean!D2:D651,Clean!M2:M651)))</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="41">
+      <c r="E16" cm="1" s="19">
         <f t="array" ref="E16">SUMPRODUCT(--NOT(EXACT(Raw!D2:D651,UPPER(LEFT(TRIM(Raw!D2:D651),1)))))</f>
         <v/>
       </c>
@@ -1573,7 +1570,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1587,7 +1584,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1639,7 @@
           <t>=IF(MID(J2,5,1)="-",DATE(LEFT(J2,4),MID(J2,6,2),MID(J2,9,2)),DATE(MID(J2,7,4),LEFT(J2,2),MID(J2,4,2)))+TIMEVALUE(MID(J2,12,8))</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="41">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">SUMPRODUCT(--(HOUR(IF(MID(Raw!J2:J651,5,1)="-",DATE(LEFT(Raw!J2:J651,4),MID(Raw!J2:J651,6,2),MID(Raw!J2:J651,9,2)),DATE(MID(Raw!J2:J651,7,4),LEFT(Raw!J2:J651,2),MID(Raw!J2:J651,4,2)))+TIMEVALUE(MID(Raw!J2:J651,12,8)))&gt;=17))</f>
         <v/>
       </c>
@@ -1671,7 +1668,7 @@
           <t>=AND(R2=MAXIFS($R$2:$R$651,$Q$2:$Q$651,Q2),COUNTIFS($Q$2:Q2,Q2,$R$2:R2,R2)=1)</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="41">
+      <c r="E6" cm="1" s="19">
         <f t="array" ref="E6">ROWS(_xlfn.UNIQUE(TEXT(VALUE(SUBSTITUTE(Raw!I2:I651,"MRN-","")),"00000000")))</f>
         <v/>
       </c>
@@ -1692,7 +1689,7 @@
           <t>Which RegisteredOn did you keep for MRN 01276260? Enter it as a date and time.</t>
         </is>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="43" t="n">
         <v>43820.5875</v>
       </c>
       <c r="D7" s="40" t="inlineStr">
@@ -1700,7 +1697,7 @@
           <t>=MAXIFS(Clean!R2:R651,Clean!Q2:Q651,"01276260",Clean!S2:S651,TRUE)</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="45">
+      <c r="E7" cm="1" s="44">
         <f t="array" ref="E7">MAX(IF(TEXT(VALUE(SUBSTITUTE(Raw!I2:I651,"MRN-","")),"00000000")="01276260",IF(MID(Raw!J2:J651,5,1)="-",DATE(LEFT(Raw!J2:J651,4),MID(Raw!J2:J651,6,2),MID(Raw!J2:J651,9,2)),DATE(MID(Raw!J2:J651,7,4),LEFT(Raw!J2:J651,2),MID(Raw!J2:J651,4,2)))+TIMEVALUE(MID(Raw!J2:J651,12,8))))</f>
         <v/>
       </c>

--- a/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
+++ b/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C36"/>
+  <dimension ref="B2:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -786,7 +786,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Intermediate  ·  about 60 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Intermediate  ·  about 145 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -1017,94 +1017,118 @@
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 650 rows</t>
+          <t>12 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 650 rows, in the Excel Table 'tblClean'</t>
+          <t>Data: 650 rows</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>PayerMap</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 19 rows, in the Excel Table 'tblPayerMap'</t>
+          <t>Data: 650 rows, in the Excel Table 'tblClean'</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>CensusExport</t>
+          <t>PayerMap</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 49 rows</t>
+          <t>Data: 19 rows, in the Excel Table 'tblPayerMap'</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>LabFeed</t>
+          <t>CensusExport</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 116 rows</t>
+          <t>Data: 49 rows</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
+          <t>LabFeed</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Data: 116 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>CleaningLog</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Data: 9 rows, in the Excel Table 'tblLog'</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="48" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>A 650-row patient registration export from Bluestone's legacy registration system (names, DOBs, phones, insurance, and MRNs typed every which way, plus duplicates), a payer mapping table, a one-week bed-board census export, and a 116-line lab interface feed from Cedar Ridge Medical Center.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>A 650-row patient registration export from Bluestone's legacy registration system (names, DOBs, phones, insurance, and MRNs typed every which way, plus duplicates), a payer mapping table, a one-week bed-board census export, and a 116-line lab interface feed from Cedar Ridge Medical Center.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -1180,7 +1204,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="126" customHeight="1">
+    <row r="5" ht="141" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>1</t>
@@ -1205,7 +1229,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>TRIM removes leading and trailing spaces and shrinks inner runs to one space, so any name it shortens had extra spaces. Comparing lengths tests all 650 rows at once: the comparison gives TRUE/FALSE for each row, the double minus turns those into 1/0, and SUMPRODUCT adds them. You can't see a trailing space by looking at a cell, so a count like this is how you find out a problem exists before you fix it. In Microsoft 365, =SUM(--(LEN(…)&lt;&gt;LEN(TRIM(…)))) works too.</t>
+          <t>TRIM removes leading and trailing spaces and shrinks inner runs to one space, so any name it shortens had extra spaces. Comparing lengths tests all 650 rows at once: the comparison gives TRUE/FALSE for each row, the double minus turns those into 1/0, and SUMPRODUCT adds them. You can't see a trailing space by looking at a cell, so a count like this is how you find out a problem exists before you fix it. In Microsoft 365 or Excel 2021+, =SUM(--(LEN(…)&lt;&gt;LEN(TRIM(…)))) works too.</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1282,7 @@
 2. Click any cell in the data, then Data → Remove Duplicates.
 3. Keep My data has headers ticked. Untick RecordID and leave the other nine columns ticked. Click OK.
 4. Excel reports 40 duplicate values found and removed; 610 unique values remain.
-Formula check without deleting anything (Microsoft 365 / Excel 2021+): =ROWS(Raw!B2:J651)-ROWS(UNIQUE(Raw!B2:J651))</t>
+Formula check without deleting anything (Microsoft 365 or Excel 2021+): =ROWS(Raw!B2:J651)-ROWS(UNIQUE(Raw!B2:J651))</t>
         </is>
       </c>
       <c r="E7" cm="1" s="19">
@@ -1326,7 +1350,7 @@
 2. In the first ZIP+4 row, O11 (Bluestone, OH 45501-8106), type 45501.
 3. Select O4, the first empty cell, and press Ctrl + E (or Data → Flash Fill).
 4. Check the result: =SUMPRODUCT(--(LEN(Clean!O2:O651)&lt;&gt;5)) should return 0. If some rows are wrong, press Ctrl + Z, type the correct ZIP on one of the wrong rows as an extra example, and run Flash Fill again.
-Formula alternative (Microsoft 365): =LEFT(TEXTAFTER(G2," ",-1),5)</t>
+Formula alternative (Microsoft 365 or Excel 2024): =LEFT(TEXTAFTER(G2," ",-1),5)</t>
         </is>
       </c>
       <c r="E9" cm="1" s="19">

--- a/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
+++ b/03-data-analysis/03-data-cleaning/3.3-data-cleaning.xlsx
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C38"/>
+  <dimension ref="B1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -769,6 +769,7 @@
     <col width="95" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -790,6 +791,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -846,6 +848,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -866,7 +869,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -874,7 +877,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type your answers to tasks 1 and 3 in its yellow cells. For tasks 2 and 4–12, do the work on the sheet the task names (Clean, CensusExport, LabFeed, or CleaningLog), and the task's gray cell on Practice reads it.</t>
         </is>
       </c>
     </row>
@@ -950,6 +953,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
@@ -1006,6 +1010,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
@@ -1034,11 +1039,11 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 650 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
+          <t>Data: 650 rows. The registration export exactly as received. Read it, but never edit it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Clean</t>
@@ -1046,11 +1051,11 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 650 rows, in the Excel Table 'tblClean'</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
+          <t>Data: 650 rows, in the Excel Table 'tblClean'. Your working copy of Raw. Fill its yellow columns: K–Q in the practice tasks, and R–S in the bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
           <t>PayerMap</t>
@@ -1058,11 +1063,11 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 19 rows, in the Excel Table 'tblPayerMap'</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
+          <t>Data: 19 rows, in the Excel Table 'tblPayerMap'. The mapping table that turns each insurance spelling into a PayerID (task 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
           <t>CensusExport</t>
@@ -1070,7 +1075,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 49 rows</t>
+          <t>Data: 49 rows. A one-week bed-board census export with blank Facility and Unit cells to fill (task 4).</t>
         </is>
       </c>
     </row>
@@ -1082,11 +1087,11 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 116 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
+          <t>Data: 116 rows. A pipe-delimited lab interface feed to split with Text to Columns (task 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
           <t>CleaningLog</t>
@@ -1094,7 +1099,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Data: 9 rows, in the Excel Table 'tblLog'</t>
+          <t>Data: 9 rows, in the Excel Table 'tblLog'. Your cleaning log. Fill in its yellow cells as you go. Task 12 checks step 2's RowsChanged cell.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1275,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Make a copy of the Raw sheet (right-click its tab → Move or Copy → tick Create a copy). On the copy, run Data → Remove Duplicates on all the data (A1:J651) with every column ticked except RecordID (each row has its own RecordID, so leaving it ticked finds nothing). How many duplicate rows does Excel remove?</t>
+          <t>Make a copy of the Raw sheet (right-click its tab → Move or Copy… → tick Create a copy). On the copy, run Data → Remove Duplicates on all the data (A1:J651) with every column ticked except RecordID (each row has its own RecordID, so leaving it ticked finds nothing). How many duplicate rows does Excel remove?</t>
         </is>
       </c>
       <c r="C7" s="39" t="n">
@@ -1312,7 +1317,7 @@
       <c r="D8" s="40" t="inlineStr">
         <is>
           <t>1. Select A2:B50 on CensusExport (not the whole columns, and not the header row).
-2. Home → Find &amp; Select → Go To Special… (or press F5, Mac: ⌃ + G, then Special…). Choose Blanks → OK. Only the empty cells stay selected.
+2. Home → Find &amp; Select → Go To Special… (or press F5, Mac: Control + G, then Special…). Choose Blanks → OK. Only the empty cells stay selected.
 3. Without clicking anywhere, type = and press ↑. The active cell is the first blank, A3, so the formula reads =A2.
 4. Press Ctrl + Enter (Mac: ⌘ + Return) to put that formula in every selected blank. Each copy points to the cell above itself.
 5. Turn the formulas into values: select A2:B50, copy, then Paste Special → Values.
@@ -1349,7 +1354,7 @@
           <t>1. In O2 type 45501 (from Bluestone OH 45501), and in O3 type 45720 (from CEDAR RIDGE, OH 45720).
 2. In the first ZIP+4 row, O11 (Bluestone, OH 45501-8106), type 45501.
 3. Select O4, the first empty cell, and press Ctrl + E (or Data → Flash Fill).
-4. Check the result: =SUMPRODUCT(--(LEN(Clean!O2:O651)&lt;&gt;5)) should return 0. If some rows are wrong, press Ctrl + Z, type the correct ZIP on one of the wrong rows as an extra example, and run Flash Fill again.
+4. Check the result: =SUMPRODUCT(--(LEN(Clean!O2:O651)&lt;&gt;5)) should return 0. If some rows are wrong, press Ctrl + Z (Mac: ⌘ + Z), type the correct ZIP on one of the wrong rows as an extra example, and run Flash Fill again.
 Formula alternative (Microsoft 365 or Excel 2024): =LEFT(TEXTAFTER(G2," ",-1),5)</t>
         </is>
       </c>
@@ -1698,7 +1703,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>The first test, RegisteredClean = MAXIFS(all RegisteredClean, all MRNClean, this MRN), is TRUE on the patient's latest row. Exact copies share that time, so the second test counts how many rows so far (the range $Q$2:Q2 grows as the formula goes down) have this MRN and this time. It equals 1 only on the first of them. The total must equal the 560 distinct MRNs from practice task 7, which is a good cross-check. Avoid comparing date-times with "&gt;"&amp;R2 inside COUNTIFS, because that turns the time into text with 15 digits and can miss by a rounding error.</t>
+          <t>The first test, RegisteredClean = MAXIFS(all RegisteredClean, all MRNClean, this MRN), is TRUE on the patient's latest row. Exact copies share that time, so the second test counts how many rows so far (the expanding range $Q$2:Q2 grows as the formula goes down) have this MRN and this time. It equals 1 only on the first of them. The total must equal the 560 distinct MRNs from practice task 7, which is a good cross-check. Avoid comparing date-times with "&gt;"&amp;R2 inside COUNTIFS, because that turns the time into text with 15 digits and can miss by a rounding error.</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1839,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
+          <t>For tasks 1 and 3, type a formula or value in the yellow cell. For the other tasks, do the work on the sheet the task names, and the gray cell here reads it. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1923,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="66" customHeight="1">
+    <row r="8" ht="81" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>3</t>
@@ -1926,7 +1931,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Make a copy of the Raw sheet (right-click its tab → Move or Copy → tick Create a copy). On the copy, run Data → Remove Duplicates on all the data (A1:J651) with every column ticked except RecordID (each row has its own RecordID, so leaving it ticked finds nothing). How many duplicate rows does Excel remove?</t>
+          <t>Make a copy of the Raw sheet (right-click its tab → Move or Copy… → tick Create a copy). On the copy, run Data → Remove Duplicates on all the data (A1:J651) with every column ticked except RecordID (each row has its own RecordID, so leaving it ticked finds nothing). How many duplicate rows does Excel remove?</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -76192,10 +76197,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="49" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>For B1 and B2, fill the yellow RegisteredClean and Keep columns on the Clean sheet, and the gray cell here reads them. For B3–B5, type a formula or value in the yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
         </is>
       </c>
     </row>
